--- a/data/trans_camb/P23_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 12,73</t>
+          <t>-3,7; 13,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 3,56</t>
+          <t>-12,44; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 15,13</t>
+          <t>-1,2; 14,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 5,62</t>
+          <t>-9,59; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,53</t>
+          <t>-0,73; 11,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 1,71</t>
+          <t>-9,01; 2,11</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 34,7</t>
+          <t>-8,19; 36,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 9,49</t>
+          <t>-27,77; 10,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 64,33</t>
+          <t>-4,0; 65,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 23,06</t>
+          <t>-30,42; 23,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 36,06</t>
+          <t>-2,05; 34,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 5,65</t>
+          <t>-24,02; 6,41</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 9,31</t>
+          <t>-4,9; 8,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 9,21</t>
+          <t>-5,06; 8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 11,02</t>
+          <t>-0,08; 10,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 8,94</t>
+          <t>-1,7; 9,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 8,29</t>
+          <t>-0,7; 7,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,5</t>
+          <t>-1,11; 7,79</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 26,07</t>
+          <t>-11,4; 24,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 25,91</t>
+          <t>-12,01; 24,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 52,13</t>
+          <t>-0,4; 52,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 42,86</t>
+          <t>-6,21; 45,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 28,15</t>
+          <t>-2,01; 27,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 26,25</t>
+          <t>-3,79; 26,8</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 0,12</t>
+          <t>-15,15; 0,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,16; -9,03</t>
+          <t>-23,5; -8,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,29</t>
+          <t>-9,36; 4,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 2,95</t>
+          <t>-11,43; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,8</t>
+          <t>-10,02; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,92; -5,07</t>
+          <t>-14,6; -4,71</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 0,67</t>
+          <t>-29,95; 2,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,74; -20,83</t>
+          <t>-47,3; -19,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 16,92</t>
+          <t>-29,36; 19,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 11,18</t>
+          <t>-36,08; 9,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 2,05</t>
+          <t>-25,14; 1,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,39; -14,33</t>
+          <t>-37,13; -13,88</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -4,79</t>
+          <t>-19,37; -4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,6; -1,28</t>
+          <t>-16,16; -1,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 4,55</t>
+          <t>-8,21; 5,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 6,67</t>
+          <t>-6,58; 6,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -1,89</t>
+          <t>-11,31; -1,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,02</t>
+          <t>-9,39; 0,66</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -11,39</t>
+          <t>-37,87; -10,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,54; -2,51</t>
+          <t>-31,65; -3,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 17,58</t>
+          <t>-25,44; 20,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 27,92</t>
+          <t>-21,5; 24,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,24; -5,51</t>
+          <t>-28,16; -3,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 0,45</t>
+          <t>-23,62; 1,72</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 12,04</t>
+          <t>-8,69; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 9,16</t>
+          <t>-11,35; 8,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 10,81</t>
+          <t>-7,64; 9,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 6,0</t>
+          <t>-11,05; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 8,48</t>
+          <t>-5,25; 7,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 4,51</t>
+          <t>-8,88; 4,51</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 32,52</t>
+          <t>-18,91; 31,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 24,78</t>
+          <t>-24,7; 22,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 45,18</t>
+          <t>-23,83; 41,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 24,95</t>
+          <t>-33,46; 22,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 26,59</t>
+          <t>-13,74; 25,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 13,49</t>
+          <t>-23,22; 14,48</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -7,45</t>
+          <t>-24,43; -7,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -3,77</t>
+          <t>-20,64; -3,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,67</t>
+          <t>-6,56; 7,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 10,11</t>
+          <t>-3,82; 10,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -2,1</t>
+          <t>-12,94; -2,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 1,54</t>
+          <t>-10,04; 0,98</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,16; -17,41</t>
+          <t>-47,99; -16,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -9,18</t>
+          <t>-41,22; -8,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 38,46</t>
+          <t>-24,65; 37,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 52,23</t>
+          <t>-14,71; 52,34</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,87; -6,42</t>
+          <t>-34,57; -7,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 4,34</t>
+          <t>-27,27; 2,88</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 10,24</t>
+          <t>-2,04; 9,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -1,67</t>
+          <t>-12,55; -1,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,6</t>
+          <t>-2,0; 8,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,59</t>
+          <t>-4,56; 5,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 7,42</t>
+          <t>-0,15; 7,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 0,33</t>
+          <t>-7,06; -0,07</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 29,34</t>
+          <t>-4,83; 25,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -4,7</t>
+          <t>-30,73; -4,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 33,05</t>
+          <t>-7,21; 36,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 20,09</t>
+          <t>-16,37; 24,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 25,43</t>
+          <t>-0,04; 25,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 1,1</t>
+          <t>-21,39; -0,22</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,66</t>
+          <t>-10,03; 0,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -4,73</t>
+          <t>-15,21; -4,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,96</t>
+          <t>-2,5; 5,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,38</t>
+          <t>-2,26; 6,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 1,79</t>
+          <t>-4,98; 1,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -0,33</t>
+          <t>-7,03; -0,28</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 1,64</t>
+          <t>-22,21; 1,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -11,45</t>
+          <t>-33,63; -11,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 27,27</t>
+          <t>-9,5; 27,45</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 29,91</t>
+          <t>-8,63; 31,18</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 5,85</t>
+          <t>-14,16; 5,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,31; -1,24</t>
+          <t>-20,35; -0,83</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,21</t>
+          <t>-5,37; -0,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,55; -4,83</t>
+          <t>-9,69; -4,85</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,18</t>
+          <t>-0,19; 4,16</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,69</t>
+          <t>-1,59; 2,75</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,26</t>
+          <t>-1,89; 1,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,78</t>
+          <t>-4,85; -1,62</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -0,51</t>
+          <t>-12,26; -0,99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-21,85; -11,62</t>
+          <t>-22,03; -11,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 17,14</t>
+          <t>-0,77; 17,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,86</t>
+          <t>-5,86; 11,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,84</t>
+          <t>-5,48; 3,81</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,66; -5,37</t>
+          <t>-14,05; -4,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P23_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P23_R-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 13,61</t>
+          <t>-3,37; 12,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 3,62</t>
+          <t>-12,69; 4,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,96</t>
+          <t>-1,83; 14,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 5,51</t>
+          <t>-9,17; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 11,11</t>
+          <t>-0,38; 11,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 2,11</t>
+          <t>-9,07; 2,04</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 36,7</t>
+          <t>-7,64; 32,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 10,01</t>
+          <t>-27,73; 11,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 65,22</t>
+          <t>-6,16; 62,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 23,45</t>
+          <t>-29,49; 25,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 34,46</t>
+          <t>-1,49; 35,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 6,41</t>
+          <t>-24,19; 6,39</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 8,6</t>
+          <t>-3,37; 8,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 8,6</t>
+          <t>-3,55; 9,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,87</t>
+          <t>0,05; 10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 9,31</t>
+          <t>-1,66; 9,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,84</t>
+          <t>-1,3; 7,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,79</t>
+          <t>-1,03; 7,36</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 24,73</t>
+          <t>-8,07; 25,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 24,2</t>
+          <t>-8,45; 27,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 52,61</t>
+          <t>0,42; 51,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 45,82</t>
+          <t>-6,09; 44,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 27,3</t>
+          <t>-3,72; 28,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 26,8</t>
+          <t>-2,66; 25,84</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 0,84</t>
+          <t>-15,03; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,5; -8,46</t>
+          <t>-23,97; -8,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 4,58</t>
+          <t>-10,15; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,34</t>
+          <t>-10,69; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,34</t>
+          <t>-10,01; 0,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -4,71</t>
+          <t>-14,99; -5,08</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 2,28</t>
+          <t>-30,28; 2,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,3; -19,87</t>
+          <t>-47,42; -20,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 19,46</t>
+          <t>-31,7; 16,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 9,87</t>
+          <t>-34,37; 12,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 1,06</t>
+          <t>-24,9; 1,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,13; -13,88</t>
+          <t>-37,48; -14,84</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -4,64</t>
+          <t>-19,96; -5,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -1,68</t>
+          <t>-16,16; -1,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 5,02</t>
+          <t>-7,88; 5,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 6,28</t>
+          <t>-6,67; 6,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -1,39</t>
+          <t>-11,91; -2,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 0,66</t>
+          <t>-9,29; 0,47</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,87; -10,19</t>
+          <t>-39,27; -12,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -3,7</t>
+          <t>-31,77; -3,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 20,63</t>
+          <t>-25,28; 21,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 24,47</t>
+          <t>-20,81; 25,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,16; -3,83</t>
+          <t>-29,65; -5,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 1,72</t>
+          <t>-23,41; 1,61</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 11,6</t>
+          <t>-9,22; 11,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 8,03</t>
+          <t>-10,26; 9,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 9,86</t>
+          <t>-7,91; 10,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 5,39</t>
+          <t>-11,92; 5,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 7,84</t>
+          <t>-4,79; 8,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 4,51</t>
+          <t>-7,76; 4,7</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 31,12</t>
+          <t>-19,68; 32,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 22,1</t>
+          <t>-21,08; 24,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 41,69</t>
+          <t>-23,58; 43,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,46; 22,03</t>
+          <t>-34,31; 21,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 25,53</t>
+          <t>-12,57; 25,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 14,48</t>
+          <t>-20,84; 14,88</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -7,13</t>
+          <t>-24,26; -7,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -3,52</t>
+          <t>-20,59; -4,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,58</t>
+          <t>-7,22; 7,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 10,3</t>
+          <t>-3,23; 10,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -2,29</t>
+          <t>-12,89; -2,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 0,98</t>
+          <t>-9,79; 1,36</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,99; -16,54</t>
+          <t>-47,94; -17,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,22; -8,79</t>
+          <t>-40,95; -10,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 37,5</t>
+          <t>-26,01; 35,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 52,34</t>
+          <t>-12,34; 55,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -7,01</t>
+          <t>-34,63; -6,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 2,88</t>
+          <t>-26,25; 4,2</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,29</t>
+          <t>-1,26; 9,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -1,61</t>
+          <t>-13,01; -1,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,02</t>
+          <t>-2,04; 7,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 5,32</t>
+          <t>-4,52; 5,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,26</t>
+          <t>-0,61; 6,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -0,07</t>
+          <t>-7,3; 0,09</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 25,96</t>
+          <t>-2,94; 28,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-30,73; -4,42</t>
+          <t>-31,82; -5,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 36,12</t>
+          <t>-7,15; 34,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 24,46</t>
+          <t>-16,38; 22,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 25,04</t>
+          <t>-1,82; 22,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,39; -0,22</t>
+          <t>-21,97; 0,12</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 0,63</t>
+          <t>-9,87; 0,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -4,66</t>
+          <t>-14,73; -4,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,79</t>
+          <t>-3,44; 5,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 6,67</t>
+          <t>-2,08; 6,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,83</t>
+          <t>-5,02; 2,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -0,28</t>
+          <t>-7,35; -0,37</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 1,52</t>
+          <t>-21,81; 1,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,63; -11,32</t>
+          <t>-32,65; -11,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 27,45</t>
+          <t>-12,93; 25,64</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 31,18</t>
+          <t>-8,35; 31,39</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 5,88</t>
+          <t>-14,49; 6,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,35; -0,83</t>
+          <t>-21,16; -1,21</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -0,41</t>
+          <t>-5,41; -0,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -4,85</t>
+          <t>-9,64; -4,95</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,16</t>
+          <t>-0,55; 3,97</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,75</t>
+          <t>-1,48; 2,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,26</t>
+          <t>-2,02; 1,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -1,62</t>
+          <t>-4,98; -1,66</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -0,99</t>
+          <t>-12,23; -1,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -11,57</t>
+          <t>-22,01; -11,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 17,04</t>
+          <t>-1,97; 16,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,33</t>
+          <t>-5,61; 11,17</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,81</t>
+          <t>-5,87; 3,89</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,95</t>
+          <t>-14,51; -4,96</t>
         </is>
       </c>
     </row>
